--- a/aaa.xlsx
+++ b/aaa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="314">
   <si>
     <t>Пробная площадка № 1 (ПП1)</t>
   </si>
@@ -22,43 +22,43 @@
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>Пробная площадка № 2 (ПП2)</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>14</t>
@@ -72,30 +72,30 @@
 (песок)</t>
   </si>
   <si>
+    <t>1,0-2,0
+(суглинок)</t>
+  </si>
+  <si>
+    <t>2,0-3,0
+(суглинок)</t>
+  </si>
+  <si>
+    <t>3,0-4,0
+(суглинок)</t>
+  </si>
+  <si>
+    <t>4,0-5,0
+(суглинок)</t>
+  </si>
+  <si>
+    <t>5,0-6,0
+(песок)</t>
+  </si>
+  <si>
     <t>0,2-1,0
 (суглинок)</t>
   </si>
   <si>
-    <t>1,0-2,0
-(суглинок)</t>
-  </si>
-  <si>
-    <t>2,0-3,0
-(суглинок)</t>
-  </si>
-  <si>
-    <t>3,0-4,0
-(суглинок)</t>
-  </si>
-  <si>
-    <t>4,0-5,0
-(суглинок)</t>
-  </si>
-  <si>
-    <t>5,0-6,0
-(песок)</t>
-  </si>
-  <si>
     <t>5,0-6,0
 (супесь)</t>
   </si>
@@ -106,72 +106,72 @@
     <t>6,6</t>
   </si>
   <si>
+    <t>7,8</t>
+  </si>
+  <si>
+    <t>6,3</t>
+  </si>
+  <si>
+    <t>5,9</t>
+  </si>
+  <si>
+    <t>6,7</t>
+  </si>
+  <si>
+    <t>7,1</t>
+  </si>
+  <si>
+    <t>6,9</t>
+  </si>
+  <si>
     <t>6,5</t>
   </si>
   <si>
-    <t>7,8</t>
-  </si>
-  <si>
-    <t>7,1</t>
-  </si>
-  <si>
-    <t>6,3</t>
-  </si>
-  <si>
-    <t>6,7</t>
-  </si>
-  <si>
-    <t>5,9</t>
-  </si>
-  <si>
     <t>6,4</t>
   </si>
   <si>
-    <t>6,9</t>
-  </si>
-  <si>
     <t>0,085</t>
   </si>
   <si>
     <t>4.250</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0,0220</t>
+  </si>
+  <si>
+    <t>1.100</t>
+  </si>
+  <si>
+    <t>0,0146</t>
+  </si>
+  <si>
+    <t>0.730</t>
+  </si>
+  <si>
+    <t>&lt;0,005</t>
+  </si>
+  <si>
     <t>0,064</t>
   </si>
   <si>
     <t>3.200</t>
   </si>
   <si>
-    <t>0,0220</t>
-  </si>
-  <si>
-    <t>1.100</t>
-  </si>
-  <si>
     <t>0,035</t>
   </si>
   <si>
     <t>1.750</t>
   </si>
   <si>
-    <t>0,0146</t>
-  </si>
-  <si>
-    <t>0.730</t>
-  </si>
-  <si>
     <t>0,0193</t>
   </si>
   <si>
     <t>0.965</t>
   </si>
   <si>
-    <t>&lt;0,005</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>26,2</t>
   </si>
   <si>
@@ -181,6 +181,60 @@
     <t>1.456</t>
   </si>
   <si>
+    <t>32,1</t>
+  </si>
+  <si>
+    <t>0.973</t>
+  </si>
+  <si>
+    <t>1.783</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>2.111</t>
+  </si>
+  <si>
+    <t>27,8</t>
+  </si>
+  <si>
+    <t>0.211</t>
+  </si>
+  <si>
+    <t>1.544</t>
+  </si>
+  <si>
+    <t>22,3</t>
+  </si>
+  <si>
+    <t>0.169</t>
+  </si>
+  <si>
+    <t>1.239</t>
+  </si>
+  <si>
+    <t>18,2</t>
+  </si>
+  <si>
+    <t>0.138</t>
+  </si>
+  <si>
+    <t>1.011</t>
+  </si>
+  <si>
+    <t>14,8</t>
+  </si>
+  <si>
+    <t>0.448</t>
+  </si>
+  <si>
+    <t>0.822</t>
+  </si>
+  <si>
     <t>37</t>
   </si>
   <si>
@@ -190,15 +244,6 @@
     <t>2.056</t>
   </si>
   <si>
-    <t>32,1</t>
-  </si>
-  <si>
-    <t>0.973</t>
-  </si>
-  <si>
-    <t>1.783</t>
-  </si>
-  <si>
     <t>29,6</t>
   </si>
   <si>
@@ -208,15 +253,6 @@
     <t>1.644</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>0.288</t>
-  </si>
-  <si>
-    <t>2.111</t>
-  </si>
-  <si>
     <t>27,1</t>
   </si>
   <si>
@@ -226,15 +262,6 @@
     <t>1.506</t>
   </si>
   <si>
-    <t>27,8</t>
-  </si>
-  <si>
-    <t>0.211</t>
-  </si>
-  <si>
-    <t>1.544</t>
-  </si>
-  <si>
     <t>26,8</t>
   </si>
   <si>
@@ -244,15 +271,6 @@
     <t>1.489</t>
   </si>
   <si>
-    <t>22,3</t>
-  </si>
-  <si>
-    <t>0.169</t>
-  </si>
-  <si>
-    <t>1.239</t>
-  </si>
-  <si>
     <t>24,2</t>
   </si>
   <si>
@@ -262,15 +280,6 @@
     <t>1.344</t>
   </si>
   <si>
-    <t>18,2</t>
-  </si>
-  <si>
-    <t>0.138</t>
-  </si>
-  <si>
-    <t>1.011</t>
-  </si>
-  <si>
     <t>20,3</t>
   </si>
   <si>
@@ -280,15 +289,6 @@
     <t>1.128</t>
   </si>
   <si>
-    <t>14,8</t>
-  </si>
-  <si>
-    <t>0.448</t>
-  </si>
-  <si>
-    <t>0.822</t>
-  </si>
-  <si>
     <t>18,6</t>
   </si>
   <si>
@@ -307,6 +307,51 @@
     <t>3.898</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0.909</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>0.668</t>
+  </si>
+  <si>
+    <t>3.411</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>0.286</t>
+  </si>
+  <si>
+    <t>1.462</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>0.245</t>
+  </si>
+  <si>
+    <t>1.253</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>1.114</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
@@ -316,15 +361,6 @@
     <t>2.204</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>0.909</t>
-  </si>
-  <si>
-    <t>1.16</t>
-  </si>
-  <si>
     <t>81</t>
   </si>
   <si>
@@ -334,15 +370,6 @@
     <t>1.879</t>
   </si>
   <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>0.668</t>
-  </si>
-  <si>
-    <t>3.411</t>
-  </si>
-  <si>
     <t>76</t>
   </si>
   <si>
@@ -352,15 +379,6 @@
     <t>1.763</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>0.286</t>
-  </si>
-  <si>
-    <t>1.462</t>
-  </si>
-  <si>
     <t>68</t>
   </si>
   <si>
@@ -370,15 +388,6 @@
     <t>1.578</t>
   </si>
   <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>0.245</t>
-  </si>
-  <si>
-    <t>1.253</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -388,15 +397,6 @@
     <t>1.206</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>0.218</t>
-  </si>
-  <si>
-    <t>1.114</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
@@ -424,18 +424,60 @@
     <t>1.073</t>
   </si>
   <si>
+    <t>0.847</t>
+  </si>
+  <si>
+    <t>1.418</t>
+  </si>
+  <si>
+    <t>15,4</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>0.806</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>0.549</t>
+  </si>
+  <si>
+    <t>7,4</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>0.387</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>0.319</t>
+  </si>
+  <si>
+    <t>9,9</t>
+  </si>
+  <si>
+    <t>0.518</t>
+  </si>
+  <si>
     <t>0.756</t>
   </si>
   <si>
     <t>1.266</t>
   </si>
   <si>
-    <t>0.847</t>
-  </si>
-  <si>
-    <t>1.418</t>
-  </si>
-  <si>
     <t>16,2</t>
   </si>
   <si>
@@ -445,30 +487,12 @@
     <t>0.848</t>
   </si>
   <si>
-    <t>15,4</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>0.806</t>
-  </si>
-  <si>
     <t>0.114</t>
   </si>
   <si>
     <t>0.774</t>
   </si>
   <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>0.549</t>
-  </si>
-  <si>
     <t>12,0</t>
   </si>
   <si>
@@ -478,15 +502,6 @@
     <t>0.628</t>
   </si>
   <si>
-    <t>7,4</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>0.387</t>
-  </si>
-  <si>
     <t>9,8</t>
   </si>
   <si>
@@ -496,15 +511,6 @@
     <t>0.513</t>
   </si>
   <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>0.319</t>
-  </si>
-  <si>
     <t>8,5</t>
   </si>
   <si>
@@ -514,12 +520,6 @@
     <t>0.445</t>
   </si>
   <si>
-    <t>9,9</t>
-  </si>
-  <si>
-    <t>0.518</t>
-  </si>
-  <si>
     <t>6,8</t>
   </si>
   <si>
@@ -538,6 +538,27 @@
     <t>0.765</t>
   </si>
   <si>
+    <t>0,150</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>0.882</t>
+  </si>
+  <si>
+    <t>0,126</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>0.741</t>
+  </si>
+  <si>
+    <t>&lt;0,10</t>
+  </si>
+  <si>
     <t>0,175</t>
   </si>
   <si>
@@ -547,27 +568,6 @@
     <t>1.029</t>
   </si>
   <si>
-    <t>0,150</t>
-  </si>
-  <si>
-    <t>0.300</t>
-  </si>
-  <si>
-    <t>0.882</t>
-  </si>
-  <si>
-    <t>&lt;0,10</t>
-  </si>
-  <si>
-    <t>0,126</t>
-  </si>
-  <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>0.741</t>
-  </si>
-  <si>
     <t>26,6</t>
   </si>
   <si>
@@ -577,6 +577,54 @@
     <t>1.739</t>
   </si>
   <si>
+    <t>0.930</t>
+  </si>
+  <si>
+    <t>1.216</t>
+  </si>
+  <si>
+    <t>25,9</t>
+  </si>
+  <si>
+    <t>0.324</t>
+  </si>
+  <si>
+    <t>1.693</t>
+  </si>
+  <si>
+    <t>23,4</t>
+  </si>
+  <si>
+    <t>0.292</t>
+  </si>
+  <si>
+    <t>1.529</t>
+  </si>
+  <si>
+    <t>0.256</t>
+  </si>
+  <si>
+    <t>1.34</t>
+  </si>
+  <si>
+    <t>17,5</t>
+  </si>
+  <si>
+    <t>0.219</t>
+  </si>
+  <si>
+    <t>1.144</t>
+  </si>
+  <si>
+    <t>15,6</t>
+  </si>
+  <si>
+    <t>0.780</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
     <t>28,4</t>
   </si>
   <si>
@@ -586,12 +634,6 @@
     <t>1.856</t>
   </si>
   <si>
-    <t>0.930</t>
-  </si>
-  <si>
-    <t>1.216</t>
-  </si>
-  <si>
     <t>23,2</t>
   </si>
   <si>
@@ -601,15 +643,6 @@
     <t>1.516</t>
   </si>
   <si>
-    <t>25,9</t>
-  </si>
-  <si>
-    <t>0.324</t>
-  </si>
-  <si>
-    <t>1.693</t>
-  </si>
-  <si>
     <t>24,1</t>
   </si>
   <si>
@@ -619,15 +652,6 @@
     <t>1.575</t>
   </si>
   <si>
-    <t>23,4</t>
-  </si>
-  <si>
-    <t>0.292</t>
-  </si>
-  <si>
-    <t>1.529</t>
-  </si>
-  <si>
     <t>24,5</t>
   </si>
   <si>
@@ -637,42 +661,18 @@
     <t>1.601</t>
   </si>
   <si>
-    <t>0.256</t>
-  </si>
-  <si>
-    <t>1.34</t>
-  </si>
-  <si>
     <t>19,6</t>
   </si>
   <si>
     <t>1.281</t>
   </si>
   <si>
-    <t>17,5</t>
-  </si>
-  <si>
-    <t>0.219</t>
-  </si>
-  <si>
-    <t>1.144</t>
-  </si>
-  <si>
     <t>0.227</t>
   </si>
   <si>
     <t>1.19</t>
   </si>
   <si>
-    <t>15,6</t>
-  </si>
-  <si>
-    <t>0.780</t>
-  </si>
-  <si>
-    <t>1.02</t>
-  </si>
-  <si>
     <t>0.740</t>
   </si>
   <si>
@@ -685,6 +685,45 @@
     <t>2.824</t>
   </si>
   <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>0.900</t>
+  </si>
+  <si>
+    <t>0.687</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
+    <t>0.520</t>
+  </si>
+  <si>
+    <t>1.985</t>
+  </si>
+  <si>
+    <t>1,9</t>
+  </si>
+  <si>
+    <t>0.190</t>
+  </si>
+  <si>
+    <t>0.725</t>
+  </si>
+  <si>
+    <t>0.180</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>0.850</t>
+  </si>
+  <si>
+    <t>0.649</t>
+  </si>
+  <si>
     <t>2,5</t>
   </si>
   <si>
@@ -694,15 +733,6 @@
     <t>0.954</t>
   </si>
   <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>0.900</t>
-  </si>
-  <si>
-    <t>0.687</t>
-  </si>
-  <si>
     <t>2,3</t>
   </si>
   <si>
@@ -712,39 +742,18 @@
     <t>0.878</t>
   </si>
   <si>
-    <t>5,2</t>
-  </si>
-  <si>
-    <t>0.520</t>
-  </si>
-  <si>
-    <t>1.985</t>
-  </si>
-  <si>
     <t>2,6</t>
   </si>
   <si>
     <t>0.992</t>
   </si>
   <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>0.190</t>
-  </si>
-  <si>
-    <t>0.725</t>
-  </si>
-  <si>
     <t>3,5</t>
   </si>
   <si>
     <t>1.336</t>
   </si>
   <si>
-    <t>0.180</t>
-  </si>
-  <si>
     <t>1,5</t>
   </si>
   <si>
@@ -754,15 +763,6 @@
     <t>0.573</t>
   </si>
   <si>
-    <t>1,7</t>
-  </si>
-  <si>
-    <t>0.850</t>
-  </si>
-  <si>
-    <t>0.649</t>
-  </si>
-  <si>
     <t>1,4</t>
   </si>
   <si>
@@ -781,6 +781,57 @@
     <t>4.667</t>
   </si>
   <si>
+    <t>0,095</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>3.167</t>
+  </si>
+  <si>
+    <t>0,056</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>1.867</t>
+  </si>
+  <si>
+    <t>0,0140</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>0.467</t>
+  </si>
+  <si>
+    <t>0,0113</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.377</t>
+  </si>
+  <si>
+    <t>0,0083</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>0.277</t>
+  </si>
+  <si>
+    <t>0,0080</t>
+  </si>
+  <si>
+    <t>0.267</t>
+  </si>
+  <si>
     <t>0,072</t>
   </si>
   <si>
@@ -790,15 +841,6 @@
     <t>2.4</t>
   </si>
   <si>
-    <t>0,095</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>3.167</t>
-  </si>
-  <si>
     <t>0,051</t>
   </si>
   <si>
@@ -808,30 +850,12 @@
     <t>1.7</t>
   </si>
   <si>
-    <t>0,056</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>1.867</t>
-  </si>
-  <si>
     <t>0.017</t>
   </si>
   <si>
     <t>1.167</t>
   </si>
   <si>
-    <t>0,0140</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>0.467</t>
-  </si>
-  <si>
     <t>0,0170</t>
   </si>
   <si>
@@ -841,15 +865,6 @@
     <t>0.567</t>
   </si>
   <si>
-    <t>0,0113</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.377</t>
-  </si>
-  <si>
     <t>0,0127</t>
   </si>
   <si>
@@ -859,27 +874,12 @@
     <t>0.423</t>
   </si>
   <si>
-    <t>0,0083</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>0.277</t>
-  </si>
-  <si>
     <t>0,0094</t>
   </si>
   <si>
     <t>0.313</t>
   </si>
   <si>
-    <t>0,0080</t>
-  </si>
-  <si>
-    <t>0.267</t>
-  </si>
-  <si>
     <t>0,0062</t>
   </si>
   <si>
@@ -895,37 +895,76 @@
     <t>0.452</t>
   </si>
   <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>0.158</t>
+  </si>
+  <si>
+    <t>&lt;5</t>
+  </si>
+  <si>
+    <t>11,0</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
     <t>0.105</t>
   </si>
   <si>
-    <t>306</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>0.158</t>
-  </si>
-  <si>
     <t>24,0</t>
   </si>
   <si>
-    <t>&lt;5</t>
-  </si>
-  <si>
     <t>5,3</t>
   </si>
   <si>
-    <t>11,0</t>
-  </si>
-  <si>
-    <t>0.011</t>
+    <t>10.66</t>
+  </si>
+  <si>
+    <t>4.74</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>2.54</t>
+  </si>
+  <si>
+    <t>1.83</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>5.81</t>
+  </si>
+  <si>
+    <t>3.74</t>
+  </si>
+  <si>
+    <t>3.01</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>1.03</t>
   </si>
 </sst>
 </file>
@@ -1367,13 +1406,16 @@
         <v>181</v>
       </c>
       <c r="K3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L3" t="s">
         <v>249</v>
       </c>
       <c r="M3" t="s">
         <v>288</v>
+      </c>
+      <c r="N3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1405,10 +1447,13 @@
         <v>289</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:14">
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
       <c r="F5" t="s">
         <v>51</v>
       </c>
@@ -1431,23 +1476,23 @@
         <v>251</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
@@ -1456,7 +1501,7 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
         <v>52</v>
@@ -1471,7 +1516,7 @@
         <v>171</v>
       </c>
       <c r="J7" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s">
         <v>220</v>
@@ -1482,10 +1527,13 @@
       <c r="M7" t="s">
         <v>290</v>
       </c>
+      <c r="N7" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="E8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -1500,7 +1548,7 @@
         <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K8" t="s">
         <v>221</v>
@@ -1509,13 +1557,16 @@
         <v>253</v>
       </c>
       <c r="M8" t="s">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="N8" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:14">
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
       <c r="F9" t="s">
         <v>54</v>
       </c>
@@ -1529,7 +1580,7 @@
         <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K9" t="s">
         <v>222</v>
@@ -1538,10 +1589,10 @@
         <v>254</v>
       </c>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1551,10 +1602,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -1563,7 +1614,7 @@
         <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -1572,13 +1623,13 @@
         <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="I11" t="s">
         <v>174</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="K11" t="s">
         <v>223</v>
@@ -1587,12 +1638,15 @@
         <v>255</v>
       </c>
       <c r="M11" t="s">
-        <v>292</v>
+        <v>291</v>
+      </c>
+      <c r="N11" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="E12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -1601,7 +1655,7 @@
         <v>98</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
         <v>175</v>
@@ -1616,13 +1670,16 @@
         <v>256</v>
       </c>
       <c r="M12" t="s">
-        <v>202</v>
+        <v>292</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:14">
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
       <c r="F13" t="s">
         <v>57</v>
       </c>
@@ -1630,7 +1687,7 @@
         <v>99</v>
       </c>
       <c r="H13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I13" t="s">
         <v>176</v>
@@ -1645,23 +1702,23 @@
         <v>257</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
@@ -1670,7 +1727,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
@@ -1679,7 +1736,7 @@
         <v>100</v>
       </c>
       <c r="H15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s">
         <v>177</v>
@@ -1696,10 +1753,13 @@
       <c r="M15" t="s">
         <v>293</v>
       </c>
+      <c r="N15" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="E16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
         <v>59</v>
@@ -1708,10 +1768,10 @@
         <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
         <v>190</v>
@@ -1723,13 +1783,16 @@
         <v>259</v>
       </c>
       <c r="M16" t="s">
-        <v>256</v>
+        <v>37</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:14">
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
       <c r="F17" t="s">
         <v>60</v>
       </c>
@@ -1737,10 +1800,10 @@
         <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s">
         <v>191</v>
@@ -1752,10 +1815,10 @@
         <v>260</v>
       </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N17" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1765,10 +1828,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
@@ -1777,7 +1840,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
         <v>61</v>
@@ -1786,27 +1849,30 @@
         <v>103</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J19" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="K19" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s">
         <v>261</v>
       </c>
       <c r="M19" t="s">
-        <v>294</v>
+        <v>293</v>
+      </c>
+      <c r="N19" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="E20" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -1815,28 +1881,31 @@
         <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I20" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s">
         <v>262</v>
       </c>
       <c r="M20" t="s">
-        <v>295</v>
+        <v>37</v>
       </c>
       <c r="N20" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:14">
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
       <c r="F21" t="s">
         <v>63</v>
       </c>
@@ -1844,38 +1913,38 @@
         <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I21" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K21" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s">
         <v>263</v>
       </c>
       <c r="M21" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N21" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
@@ -1884,7 +1953,7 @@
         <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
         <v>64</v>
@@ -1893,27 +1962,30 @@
         <v>106</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="I23" t="s">
         <v>177</v>
       </c>
       <c r="J23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K23" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s">
-        <v>41</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s">
-        <v>296</v>
+        <v>293</v>
+      </c>
+      <c r="N23" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="E24" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
         <v>65</v>
@@ -1922,28 +1994,31 @@
         <v>107</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K24" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M24" t="s">
-        <v>259</v>
+        <v>37</v>
       </c>
       <c r="N24" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:14">
+      <c r="E25" t="s">
+        <v>37</v>
+      </c>
       <c r="F25" t="s">
         <v>66</v>
       </c>
@@ -1951,25 +2026,25 @@
         <v>108</v>
       </c>
       <c r="H25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K25" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="L25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N25" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1979,10 +2054,10 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
@@ -1991,97 +2066,103 @@
         <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
         <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I27" t="s">
         <v>177</v>
       </c>
       <c r="J27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s">
-        <v>297</v>
+        <v>294</v>
+      </c>
+      <c r="N27" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="E28" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
         <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K28" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s">
-        <v>48</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:14">
+      <c r="E29" t="s">
+        <v>37</v>
+      </c>
       <c r="F29" t="s">
         <v>69</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K29" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L29" t="s">
         <v>268</v>
       </c>
       <c r="M29" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N29" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2089,7 +2170,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
         <v>25</v>
@@ -2098,97 +2179,103 @@
         <v>33</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
         <v>70</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L31" t="s">
         <v>269</v>
       </c>
       <c r="M31" t="s">
-        <v>298</v>
+        <v>296</v>
+      </c>
+      <c r="N31" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="E32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
         <v>71</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
         <v>149</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="J32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="L32" t="s">
         <v>270</v>
       </c>
       <c r="M32" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="N32" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:14">
+      <c r="E33" t="s">
+        <v>37</v>
+      </c>
       <c r="F33" t="s">
         <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H33" t="s">
         <v>150</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="J33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K33" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L33" t="s">
         <v>271</v>
       </c>
       <c r="M33" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N33" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2196,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -2205,13 +2292,13 @@
         <v>31</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
         <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H35" t="s">
         <v>151</v>
@@ -2220,82 +2307,88 @@
         <v>177</v>
       </c>
       <c r="J35" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K35" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="L35" t="s">
         <v>272</v>
       </c>
       <c r="M35" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+      <c r="N35" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="E36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
         <v>74</v>
       </c>
       <c r="G36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H36" t="s">
         <v>152</v>
       </c>
       <c r="I36" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J36" t="s">
         <v>204</v>
       </c>
       <c r="K36" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L36" t="s">
         <v>273</v>
       </c>
       <c r="M36" t="s">
-        <v>48</v>
+        <v>253</v>
       </c>
       <c r="N36" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:14">
+      <c r="E37" t="s">
+        <v>37</v>
+      </c>
       <c r="F37" t="s">
         <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H37" t="s">
         <v>153</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J37" t="s">
         <v>205</v>
       </c>
       <c r="K37" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="L37" t="s">
         <v>274</v>
       </c>
       <c r="M37" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N37" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2303,13 +2396,13 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
@@ -2318,10 +2411,10 @@
         <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H39" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="I39" t="s">
         <v>177</v>
@@ -2330,13 +2423,16 @@
         <v>206</v>
       </c>
       <c r="K39" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L39" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="M39" t="s">
-        <v>297</v>
+        <v>299</v>
+      </c>
+      <c r="N39" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2347,62 +2443,65 @@
         <v>77</v>
       </c>
       <c r="G40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I40" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J40" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="K40" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M40" t="s">
-        <v>48</v>
+        <v>273</v>
       </c>
       <c r="N40" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:14">
+      <c r="E41" t="s">
+        <v>37</v>
+      </c>
       <c r="F41" t="s">
         <v>78</v>
       </c>
       <c r="G41" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I41" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K41" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M41" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N41" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2410,106 +2509,112 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
         <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I43" t="s">
         <v>177</v>
       </c>
       <c r="J43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K43" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="L43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s">
-        <v>297</v>
+        <v>300</v>
+      </c>
+      <c r="N43" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="E44" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
         <v>80</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K44" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="L44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M44" t="s">
-        <v>48</v>
+        <v>262</v>
       </c>
       <c r="N44" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:14">
+      <c r="E45" t="s">
+        <v>37</v>
+      </c>
       <c r="F45" t="s">
         <v>81</v>
       </c>
       <c r="G45" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I45" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J45" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K45" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="L45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M45" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N45" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2517,7 +2622,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
         <v>25</v>
@@ -2526,97 +2631,103 @@
         <v>33</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F47" t="s">
         <v>82</v>
       </c>
       <c r="G47" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I47" t="s">
         <v>177</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="K47" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="L47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M47" t="s">
-        <v>297</v>
+        <v>293</v>
+      </c>
+      <c r="N47" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="E48" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>83</v>
       </c>
       <c r="G48" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I48" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J48" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="K48" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="L48" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M48" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N48" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:14">
+      <c r="E49" t="s">
+        <v>37</v>
+      </c>
       <c r="F49" t="s">
         <v>84</v>
       </c>
       <c r="G49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K49" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="L49" t="s">
         <v>282</v>
       </c>
       <c r="M49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -2624,7 +2735,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
         <v>25</v>
@@ -2633,22 +2744,22 @@
         <v>34</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F51" t="s">
         <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="H51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I51" t="s">
         <v>177</v>
       </c>
       <c r="J51" t="s">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="K51" t="s">
         <v>243</v>
@@ -2657,24 +2768,27 @@
         <v>283</v>
       </c>
       <c r="M51" t="s">
-        <v>299</v>
+        <v>293</v>
+      </c>
+      <c r="N51" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="E52" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
         <v>86</v>
       </c>
       <c r="G52" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="H52" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="I52" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J52" t="s">
         <v>214</v>
@@ -2683,27 +2797,30 @@
         <v>244</v>
       </c>
       <c r="L52" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="M52" t="s">
-        <v>300</v>
+        <v>37</v>
       </c>
       <c r="N52" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:14">
+      <c r="E53" t="s">
+        <v>37</v>
+      </c>
       <c r="F53" t="s">
         <v>87</v>
       </c>
       <c r="G53" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
         <v>164</v>
       </c>
       <c r="I53" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J53" t="s">
         <v>215</v>
@@ -2715,15 +2832,15 @@
         <v>284</v>
       </c>
       <c r="M53" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N53" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2740,7 +2857,7 @@
         <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F55" t="s">
         <v>88</v>
@@ -2755,7 +2872,7 @@
         <v>177</v>
       </c>
       <c r="J55" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K55" t="s">
         <v>246</v>
@@ -2764,12 +2881,15 @@
         <v>285</v>
       </c>
       <c r="M55" t="s">
-        <v>297</v>
+        <v>293</v>
+      </c>
+      <c r="N55" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="E56" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
         <v>89</v>
@@ -2781,7 +2901,7 @@
         <v>166</v>
       </c>
       <c r="I56" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J56" t="s">
         <v>216</v>
@@ -2793,13 +2913,16 @@
         <v>286</v>
       </c>
       <c r="M56" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N56" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:14">
+      <c r="E57" t="s">
+        <v>37</v>
+      </c>
       <c r="F57" t="s">
         <v>90</v>
       </c>
@@ -2810,7 +2933,7 @@
         <v>167</v>
       </c>
       <c r="I57" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J57" t="s">
         <v>217</v>
@@ -2822,10 +2945,10 @@
         <v>287</v>
       </c>
       <c r="M57" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N57" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
